--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>275.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>275</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>200</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>175</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>09/09 17:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>12/09 16:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>150</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>150</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>125</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>10/09 15:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>140</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>09/09 17:45</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>125</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>125</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>125</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>09/09 17:45</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>125</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>125</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>110</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>10/09 16:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>110</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>09/09 17:45</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>110</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>110</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>110</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>10/09 16:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>110</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>10/09 16:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>100</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>13/09 16:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>100</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>13/09 16:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>100</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>100</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>110</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45908.07181971844</v>
+        <v>45908.07181972222</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,111 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>100</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+54,1%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45908.07181972222</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – KosiceSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>12/09 16:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+132%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45908.13073322111</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Djurgården</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Djurgårdens IF – Skellefteå AIKSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>13/09 13:15</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+54,1%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45908.07181971844</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+63,7%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45908.13073322111</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>12/09 16:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>150</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45908.13073322111</v>
+        <v>45908.13073321759</v>
       </c>
     </row>
     <row r="28">
@@ -1625,23 +1623,111 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+63,7%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45908.13073321759</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Rapperswil</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Rapperswil Jona Lakers – Langnau TigersSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>09/09 17:45</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>+63,7%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>45908.13073322111</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+73,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45908.18517286441</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | SaiPa – Ka</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SaiPa – KalPaFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>09/09 15:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+64,4%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45908.18517286441</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>09/09 17:45</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>100</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45908.18517286441</v>
+        <v>45908.18517285879</v>
       </c>
     </row>
     <row r="30">
@@ -1711,10 +1709,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>125</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1727,7 +1723,52 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45908.18517286441</v>
+        <v>45908.18517285879</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kladno – M</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Kladno – Mlada BoleslavRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>10/09 16:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+58,6%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45908.22285091283</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>10/09 16:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>110</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,232 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45908.22285091283</v>
+        <v>45908.22285091435</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Dukla Tren</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dukla Trencin – Spisska Nova VesExtraliga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>12/09 16:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+94,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45908.27336282805</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Jukurit – </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Jukurit – HIFKFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>09/09 15:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+91,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45908.27336282805</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KooKoo – A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>KooKoo – Assät PoriFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>09/09 15:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+89,9%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45908.27336282805</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kärpät Oul</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Kärpät Oulu – Sport VaasaFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>09/09 15:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+87,1%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45908.27336282805</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Pelicans L</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Pelicans Lahti – K-EspooFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>09/09 15:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+72,6%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45908.27336282805</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>125</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45908.27336282805</v>
+        <v>45908.27336282407</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>140</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45908.27336282805</v>
+        <v>45908.27336282407</v>
       </c>
     </row>
     <row r="34">
@@ -1885,10 +1881,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>140</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1901,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45908.27336282805</v>
+        <v>45908.27336282407</v>
       </c>
     </row>
     <row r="35">
@@ -1930,10 +1924,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>140</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1946,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45908.27336282805</v>
+        <v>45908.27336282407</v>
       </c>
     </row>
     <row r="36">
@@ -1975,23 +1967,111 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>125</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+72,6%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45908.27336282407</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Banska Bys</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Banska Bystrica – HKM AS ZvolenExtraliga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>12/09 15:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+164%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45908.30673234397</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | JYP Jyvask</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>JYP Jyvaskyla – Ilves TampereLiiga</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>10/09 15:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>+72,6%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>45908.27336282805</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+78,9%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45908.30673234397</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>175</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45908.30673234397</v>
+        <v>45908.30673234953</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>10/09 15:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>125</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,142 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45908.30673234397</v>
+        <v>45908.30673234953</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Frölunda H</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Frölunda HC – LinkopingsSHL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>13/09 13:15</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+73,6%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45908.35428607133</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Brynas IF </t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brynas IF – Vaxjo LakersSHL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>13/09 13:15</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+67,1%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45908.35428607133</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Fribourg G</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Fribourg Gotteron – LuganoSuisse - Suisse NLA stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>09/09 17:45</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>98.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+54,9%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45908.35428607133</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>110</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45908.35428607133</v>
+        <v>45908.35428607639</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>100</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45908.35428607133</v>
+        <v>45908.35428607639</v>
       </c>
     </row>
     <row r="41">
@@ -2186,10 +2182,8 @@
           <t>09/09 17:45</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>98.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>98</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2202,7 +2196,232 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45908.35428607133</v>
+        <v>45908.35428607639</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Berlin – D</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Berlin – Dresdner EislowenDEL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>09/09 17:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+184%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45908.39257307964</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Mhk 32 Lip</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Mhk 32 Liptovsky Mikulas – Dukla MichalovceExtraliga</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>12/09 16:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+126%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45908.39257307964</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Farjestads</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Farjestads BK – Rogle BKSHL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>13/09 16:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+76,9%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45908.39257307964</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EV Zug – S</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EV Zug – SC BernNational League A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>09/09 17:45</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+74,6%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45908.39257307964</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Luleå HF –</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Luleå HF – Malmö RedhawksSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>13/09 16:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+74,4%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45908.39257307964</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>09/09 17:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>200</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45908.39257307964</v>
+        <v>45908.3925730787</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>150</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45908.39257307964</v>
+        <v>45908.3925730787</v>
       </c>
     </row>
     <row r="44">
@@ -2315,10 +2311,8 @@
           <t>13/09 16:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>110</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2331,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45908.39257307964</v>
+        <v>45908.3925730787</v>
       </c>
     </row>
     <row r="45">
@@ -2360,10 +2354,8 @@
           <t>09/09 17:45</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>110</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2376,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45908.39257307964</v>
+        <v>45908.3925730787</v>
       </c>
     </row>
     <row r="46">
@@ -2405,10 +2397,8 @@
           <t>13/09 16:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>110</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2421,7 +2411,232 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45908.39257307964</v>
+        <v>45908.3925730787</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Twk Inn</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HC Twk Innsbruck Die Haie – Pustertal WolfeICE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+197%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45908.43309629009</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Black Wing</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Black Wings Linz – Pioneers VorarlbergICE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+149%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45908.43309629009</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | KAC Klagen</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>KAC Klagenfurt – Fehervar AV19ICE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+142%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45908.43309629009</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Bolzano – </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Bolzano – RB SalzbourgICE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+92,7%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45908.43309629009</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Olimpija L</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Olimpija Ljubljana – Spusu Vienna CapitalsICE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+78,7%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45908.43309629009</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>200</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45908.43309629009</v>
+        <v>45908.43309628472</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>175</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45908.43309629009</v>
+        <v>45908.43309628472</v>
       </c>
     </row>
     <row r="49">
@@ -2530,10 +2526,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>175</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2546,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45908.43309629009</v>
+        <v>45908.43309628472</v>
       </c>
     </row>
     <row r="50">
@@ -2575,10 +2569,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>140</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2591,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45908.43309629009</v>
+        <v>45908.43309628472</v>
       </c>
     </row>
     <row r="51">
@@ -2620,10 +2612,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>125</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2636,7 +2626,187 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45908.43309629009</v>
+        <v>45908.43309628472</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Presov </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HC Presov – HK PopradExtraliga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>12/09 16:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+201%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45908.47056584009</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Black Wing</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Black Wings Linz – Pioneers VorarlbergAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+172%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45908.47056584009</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Ceske Bude</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ceske Budejovice – Sparta PragueExtraliga</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>09/09 15:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+70,2%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45908.47056584009</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Genève-Ser</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Genève-Servette – HC Ajoie PorrentruyNational League A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>09/09 17:45</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+68,0%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45908.47056584009</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -2655,10 +2655,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>200</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45908.47056584009</v>
+        <v>45908.47056584491</v>
       </c>
     </row>
     <row r="53">
@@ -2700,10 +2698,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>175</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2716,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45908.47056584009</v>
+        <v>45908.47056584491</v>
       </c>
     </row>
     <row r="54">
@@ -2745,10 +2741,8 @@
           <t>09/09 15:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>110</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2761,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45908.47056584009</v>
+        <v>45908.47056584491</v>
       </c>
     </row>
     <row r="55">
@@ -2790,10 +2784,8 @@
           <t>09/09 17:45</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>110</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2806,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45908.47056584009</v>
+        <v>45908.47056584491</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,6 +2801,141 @@
         <v>45908.47056584491</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Innsbruck </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Innsbruck Die Haie – HC PustertalAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+234%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45908.72124098865</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KAC – Fehe</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>KAC – Fehervar AV19Autriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+155%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45908.72124098865</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Olimpija L</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Olimpija Ljubljana – Vienne CapitalsAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+105%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45908.72124098865</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>225</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45908.72124098865</v>
+        <v>45908.7212409838</v>
       </c>
     </row>
     <row r="57">
@@ -2872,10 +2870,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>175</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2888,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45908.72124098865</v>
+        <v>45908.7212409838</v>
       </c>
     </row>
     <row r="58">
@@ -2917,23 +2913,66 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" t="n">
+        <v>125</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+105%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45908.7212409838</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lukko – Ta</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Lukko – Tappara TampereFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>10/09 15:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>+105%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>45908.72124098865</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+72,1%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45908.77176898595</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-08.xlsx
+++ b/data/valuebets_database_2025-09-08.xlsx
@@ -2956,10 +2956,8 @@
           <t>10/09 15:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>125</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45908.77176898595</v>
+        <v>45908.77176898148</v>
       </c>
     </row>
   </sheetData>
